--- a/docs/メッセージ一覧.xlsx
+++ b/docs/メッセージ一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eclipse_git_wk\DictOpeProj\kmg-tool-cli\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F52F833-C0C1-4468-849A-FE471C26F96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728B25E7-4E9D-40ED-BEFB-A0686B928A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19100" yWindow="0" windowWidth="19390" windowHeight="20970" tabRatio="590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="メッセージ一覧" sheetId="5" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>番号</t>
     <rPh sb="0" eb="2">
@@ -158,6 +158,29 @@
     <t>例外発生</t>
     <rPh sb="0" eb="4">
       <t>レイガイハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期化の失敗</t>
+    <rPh sb="0" eb="3">
+      <t>ショキカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期化で例外が発生しました。</t>
+    <rPh sb="0" eb="3">
+      <t>ショキカ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハッセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -289,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -347,8 +370,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2379,7 +2405,7 @@
       <c r="B3" s="17">
         <v>9000</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D3" s="11" t="str">
@@ -2395,7 +2421,7 @@
       <c r="B4" s="17">
         <v>9001</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="14" t="s">
         <v>21</v>
       </c>
       <c r="D4" s="11" t="str">
@@ -2411,7 +2437,7 @@
       <c r="B5" s="17">
         <v>9002</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="11" t="str">
@@ -2869,11 +2895,15 @@
         <f>ROW()-2</f>
         <v>1</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="22">
+        <v>15000</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="D3" s="11" t="str">
         <f t="shared" ref="D3:D55" si="0">IF(C3="","",$D$1&amp;TEXT(B3,"00000")&amp;"="&amp;C3)</f>
-        <v/>
+        <v>KMGTOOLCLI_LOG15000=初期化の失敗</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2881,11 +2911,15 @@
         <f t="shared" ref="A4:A59" si="1">ROW()-2</f>
         <v>2</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="6"/>
+      <c r="B4" s="22">
+        <v>15001</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>24</v>
+      </c>
       <c r="D4" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>KMGTOOLCLI_LOG15001=初期化で例外が発生しました。</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2893,11 +2927,15 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="6"/>
+      <c r="B5" s="22">
+        <v>17000</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="D5" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>KMGTOOLCLI_LOG17000=初期化の失敗</v>
       </c>
     </row>
     <row r="6" spans="1:4">
